--- a/JsonConverter/ExcelFiles/Penalty.xlsx
+++ b/JsonConverter/ExcelFiles/Penalty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\ACE\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60F4121-6317-4F04-87E6-D25CABEFB251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D795792-775E-4617-9CD7-220D5060B07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22710" yWindow="2430" windowWidth="22300" windowHeight="9900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Penalty" sheetId="1" r:id="rId1"/>
@@ -25,39 +25,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="71">
   <si>
     <t>string</t>
   </si>
   <si>
     <t>string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>페널티ID</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>페널티 이름</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>페널티 영문 이름</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>발동 조건</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>지속 효과</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>penaltyName</t>
-  </si>
-  <si>
-    <t>penaltyNameEn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>penalty_01</t>
@@ -66,49 +52,220 @@
     <t>penalty_02</t>
   </si>
   <si>
-    <t>triggerCondition</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>effectDescription</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>PenaltyName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PenaltyNameEn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerSkillId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectValue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DurationRounds</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>유발 스킬ID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>유발 반복 횟수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>효과 종류</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>효과 수치</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지속 라운드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AccuracyDown</t>
+  </si>
+  <si>
+    <t>AttackPowerDown</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>penalty_03</t>
+  </si>
+  <si>
+    <t>penalty_04</t>
+  </si>
+  <si>
+    <t>penalty_05</t>
+  </si>
+  <si>
+    <t>penalty_06</t>
+  </si>
+  <si>
+    <t>penalty_07</t>
+  </si>
+  <si>
+    <t>penalty_08</t>
+  </si>
+  <si>
+    <t>penalty_09</t>
+  </si>
+  <si>
+    <t>요통</t>
+  </si>
+  <si>
+    <t>Lumbago</t>
+  </si>
+  <si>
+    <t>후두염</t>
+  </si>
+  <si>
+    <t>Laryngitis</t>
+  </si>
+  <si>
+    <t>손목터널증후군</t>
+  </si>
+  <si>
+    <t>Carpal Tunnel Syndrome</t>
+  </si>
+  <si>
+    <t>좌골신경통</t>
+  </si>
+  <si>
+    <t>Sciatica</t>
   </si>
   <si>
     <t>녹내장</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glaucoma</t>
+  </si>
+  <si>
+    <t>안검경련</t>
+  </si>
+  <si>
+    <t>Blepharospasm</t>
+  </si>
+  <si>
+    <t>Vertigo</t>
   </si>
   <si>
     <t>관절염</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Glaucoma</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Arthritis</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>명중률 감소</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력 감소</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격 행동 2회 반복 시</t>
-  </si>
-  <si>
-    <t>ID</t>
+  </si>
+  <si>
+    <t>근감소증</t>
+  </si>
+  <si>
+    <t>Sarcopenia</t>
+  </si>
+  <si>
+    <t>heroSkill_01_01</t>
+  </si>
+  <si>
+    <t>heroSkill_01_02</t>
+  </si>
+  <si>
+    <t>BuffPowerDown</t>
+  </si>
+  <si>
+    <t>heroSkill_01_03</t>
+  </si>
+  <si>
+    <t>heroSkill_02_01</t>
+  </si>
+  <si>
+    <t>SpeedDown</t>
+  </si>
+  <si>
+    <t>heroSkill_03_01</t>
+  </si>
+  <si>
+    <t>heroSkill_04_01</t>
+  </si>
+  <si>
+    <t>DebuffPowerDown</t>
+  </si>
+  <si>
+    <t>heroSkill_05_01</t>
+  </si>
+  <si>
+    <t>heroSkill_06_01</t>
+  </si>
+  <si>
+    <t>heroSkill_07_01</t>
+  </si>
+  <si>
+    <t>뱃살 튕기다 허리 삐끗해서 공격력 감소</t>
+  </si>
+  <si>
+    <t>라떼 이야기 너무 많이 해서 목 쉬어 버프 효과 감소</t>
+  </si>
+  <si>
+    <t>방패 던지다 손목 저려서 명중률 감소</t>
+  </si>
+  <si>
+    <t>킥 반복하다 다리 저려서 속도 감소</t>
+  </si>
+  <si>
+    <t>눈 침침해져 명중률 감소</t>
+  </si>
+  <si>
+    <t>노려보다 눈 떨려서 디버프 효과 감소</t>
+  </si>
+  <si>
+    <t>망치 던지다 어지러워서 명중률 감소</t>
+  </si>
+  <si>
+    <t>뿌리감기 반복하다 관절염 와서 공격력 감소</t>
+  </si>
+  <si>
+    <t>어지럼증</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>변신 중 힘 딸려서 근력 저하</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -117,20 +274,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF008000"/>
       <name val="&quot;맑은 고딕&quot;"/>
       <family val="3"/>
       <charset val="129"/>
@@ -151,6 +294,29 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="굴림"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="&quot;맑은 고딕&quot;"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -238,17 +404,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -261,19 +429,22 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 2" xfId="1" xr:uid="{9B4279F6-1D15-49E0-883C-873871B7B3C8}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -489,409 +660,756 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
+  <dimension ref="A1:S1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="30.5703125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="12.5703125" style="3"/>
+    <col min="1" max="1" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" style="2" customWidth="1"/>
+    <col min="3" max="4" width="24.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="48.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.5703125" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="12.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:19" s="13" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="13" customFormat="1" ht="12.75">
+      <c r="A2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="12"/>
+    </row>
+    <row r="3" spans="1:19" s="15" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="3">
+        <v>10</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J4" s="10"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+    </row>
+    <row r="5" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="12.75">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:15" s="12" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="13"/>
-    </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-    </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="3">
         <v>10</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-    </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-    </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-    </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1">
+      <c r="H5" s="3">
+        <v>2</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+    </row>
+    <row r="6" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="3">
+        <v>10</v>
+      </c>
+      <c r="H6" s="3">
+        <v>2</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+    </row>
+    <row r="7" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="3">
+        <v>10</v>
+      </c>
+      <c r="H7" s="3">
+        <v>2</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="3">
+        <v>10</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="3">
+        <v>10</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+    </row>
+    <row r="10" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="3">
+        <v>10</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+    </row>
+    <row r="11" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1">
+        <v>2</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+    </row>
+    <row r="12" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="5">
+        <v>2</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="5">
+        <v>10</v>
+      </c>
+      <c r="H12" s="5">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+    </row>
+    <row r="13" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+    </row>
+    <row r="14" spans="1:19" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-    </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1">
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+    </row>
+    <row r="15" spans="1:19" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-    </row>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="E26" s="5"/>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="E28" s="5"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-    </row>
-    <row r="30" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-    </row>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-    </row>
-    <row r="32" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+    </row>
+    <row r="16" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+    </row>
+    <row r="33" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+    </row>
+    <row r="34" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+    </row>
+    <row r="35" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+    </row>
+    <row r="36" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:9" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -1845,7 +2363,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/JsonConverter/ExcelFiles/Penalty.xlsx
+++ b/JsonConverter/ExcelFiles/Penalty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\ACE\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D795792-775E-4617-9CD7-220D5060B07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F466FAD3-62D0-4775-8AE5-54A2A40FE379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16130" yWindow="1900" windowWidth="20870" windowHeight="11880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Penalty" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="82">
   <si>
     <t>string</t>
   </si>
@@ -259,6 +259,41 @@
   <si>
     <t>변신 중 힘 딸려서 근력 저하</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>유발 스킬 이름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerSkillName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>뱃살튕기기</t>
+  </si>
+  <si>
+    <t>라떼는말이야</t>
+  </si>
+  <si>
+    <t>럭키방패</t>
+  </si>
+  <si>
+    <t>오십견킥</t>
+  </si>
+  <si>
+    <t>감으로쏘기</t>
+  </si>
+  <si>
+    <t>힘껏노려보기</t>
+  </si>
+  <si>
+    <t>망치날라가유</t>
+  </si>
+  <si>
+    <t>뿌리감기</t>
+  </si>
+  <si>
+    <t>아몬드가죽으면</t>
   </si>
 </sst>
 </file>
@@ -660,22 +695,23 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:S1000"/>
+  <dimension ref="A1:T1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" style="2" customWidth="1"/>
-    <col min="3" max="4" width="24.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="48.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.5703125" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="12.5703125" style="2"/>
+    <col min="3" max="3" width="24.7109375" style="2" customWidth="1"/>
+    <col min="4" max="5" width="19.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="48.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.5703125" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="12.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="13" customFormat="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:20" s="13" customFormat="1" ht="15.75" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>2</v>
       </c>
@@ -689,22 +725,25 @@
         <v>16</v>
       </c>
       <c r="E1" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="H1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="J1" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="13" customFormat="1" ht="12.75">
+    <row r="2" spans="1:20" s="13" customFormat="1" ht="12.75">
       <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
@@ -718,23 +757,26 @@
         <v>1</v>
       </c>
       <c r="E2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="12" t="s">
         <v>1</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>24</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="12"/>
-    </row>
-    <row r="3" spans="1:19" s="15" customFormat="1" ht="15.75" customHeight="1">
+      <c r="K2" s="12"/>
+    </row>
+    <row r="3" spans="1:20" s="15" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="14" t="s">
         <v>7</v>
       </c>
@@ -748,22 +790,25 @@
         <v>10</v>
       </c>
       <c r="E3" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="H3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="I3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="J3" s="14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15.75" customHeight="1">
+    <row r="4" spans="1:20" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -776,23 +821,25 @@
       <c r="D4" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="3">
         <v>2</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>10</v>
       </c>
-      <c r="H4" s="3">
+      <c r="I4" s="3">
         <v>2</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="J4" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="10"/>
-      <c r="K4" s="4"/>
+      <c r="K4" s="10"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -801,8 +848,9 @@
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
-    </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T4" s="4"/>
+    </row>
+    <row r="5" spans="1:20" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -815,22 +863,24 @@
       <c r="D5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="3">
         <v>2</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>10</v>
       </c>
-      <c r="H5" s="3">
+      <c r="I5" s="3">
         <v>2</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="J5" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -840,8 +890,9 @@
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
-    </row>
-    <row r="6" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T5" s="4"/>
+    </row>
+    <row r="6" spans="1:20" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>25</v>
       </c>
@@ -854,22 +905,24 @@
       <c r="D6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="3">
         <v>2</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>10</v>
       </c>
-      <c r="H6" s="3">
+      <c r="I6" s="3">
         <v>2</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -879,8 +932,9 @@
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
-    </row>
-    <row r="7" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T6" s="4"/>
+    </row>
+    <row r="7" spans="1:20" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
@@ -893,22 +947,24 @@
       <c r="D7" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="3">
         <v>2</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="3">
         <v>10</v>
       </c>
-      <c r="H7" s="3">
+      <c r="I7" s="3">
         <v>2</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -918,8 +974,9 @@
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
-    </row>
-    <row r="8" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T7" s="4"/>
+    </row>
+    <row r="8" spans="1:20" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>27</v>
       </c>
@@ -932,22 +989,24 @@
       <c r="D8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="3">
         <v>2</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -957,8 +1016,9 @@
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
-    </row>
-    <row r="9" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T8" s="4"/>
+    </row>
+    <row r="9" spans="1:20" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>28</v>
       </c>
@@ -971,22 +1031,24 @@
       <c r="D9" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="3">
         <v>2</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -996,8 +1058,9 @@
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
-    </row>
-    <row r="10" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T9" s="4"/>
+    </row>
+    <row r="10" spans="1:20" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>29</v>
       </c>
@@ -1010,22 +1073,24 @@
       <c r="D10" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="3">
         <v>2</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
@@ -1035,8 +1100,9 @@
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
-    </row>
-    <row r="11" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T10" s="4"/>
+    </row>
+    <row r="11" spans="1:20" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>30</v>
       </c>
@@ -1049,22 +1115,24 @@
       <c r="D11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>10</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>2</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -1074,8 +1142,9 @@
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
-    </row>
-    <row r="12" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T11" s="4"/>
+    </row>
+    <row r="12" spans="1:20" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -1088,22 +1157,24 @@
       <c r="D12" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="5">
         <v>2</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="5">
+      <c r="H12" s="5">
         <v>10</v>
       </c>
-      <c r="H12" s="5">
+      <c r="I12" s="5">
         <v>2</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="J12" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -1113,8 +1184,9 @@
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
-    </row>
-    <row r="13" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T12" s="4"/>
+    </row>
+    <row r="13" spans="1:20" ht="15.75" customHeight="1">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1124,7 +1196,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="4"/>
+      <c r="J13" s="3"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
@@ -1134,8 +1206,9 @@
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
-    </row>
-    <row r="14" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T13" s="4"/>
+    </row>
+    <row r="14" spans="1:20" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1145,7 +1218,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="4"/>
+      <c r="J14" s="1"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -1155,8 +1228,9 @@
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
-    </row>
-    <row r="15" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T14" s="4"/>
+    </row>
+    <row r="15" spans="1:20" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1166,7 +1240,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="4"/>
+      <c r="J15" s="1"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -1176,8 +1250,9 @@
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
-    </row>
-    <row r="16" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T15" s="4"/>
+    </row>
+    <row r="16" spans="1:20" ht="15.75" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -1187,8 +1262,9 @@
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
-    </row>
-    <row r="17" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J16" s="7"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1198,8 +1274,9 @@
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
-    </row>
-    <row r="18" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J17" s="7"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1209,8 +1286,9 @@
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
-    </row>
-    <row r="19" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J18" s="7"/>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" customHeight="1">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1220,8 +1298,9 @@
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
-    </row>
-    <row r="20" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J19" s="7"/>
+    </row>
+    <row r="20" spans="1:10" ht="15.75" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1231,8 +1310,9 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
-    </row>
-    <row r="21" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J20" s="7"/>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -1242,8 +1322,9 @@
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
-    </row>
-    <row r="22" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J21" s="7"/>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1253,8 +1334,9 @@
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
-    </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J22" s="7"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -1264,8 +1346,9 @@
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
-    </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J23" s="7"/>
+    </row>
+    <row r="24" spans="1:10" ht="15.75" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -1275,8 +1358,9 @@
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
-    </row>
-    <row r="25" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J24" s="7"/>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1286,8 +1370,9 @@
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
-    </row>
-    <row r="26" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J25" s="7"/>
+    </row>
+    <row r="26" spans="1:10" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -1297,8 +1382,9 @@
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
-    </row>
-    <row r="27" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -1308,8 +1394,9 @@
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
-    </row>
-    <row r="28" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J27" s="8"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -1319,8 +1406,9 @@
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
-    </row>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J28" s="8"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" customHeight="1">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -1330,8 +1418,9 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
-    </row>
-    <row r="30" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J29" s="8"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" customHeight="1">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -1341,8 +1430,9 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
-    </row>
-    <row r="31" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J30" s="8"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" customHeight="1">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -1352,8 +1442,9 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
-    </row>
-    <row r="32" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" customHeight="1">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -1363,8 +1454,9 @@
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
-    </row>
-    <row r="33" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J32" s="9"/>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -1374,8 +1466,9 @@
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
-    </row>
-    <row r="34" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J33" s="9"/>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" customHeight="1">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -1385,8 +1478,9 @@
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="9"/>
-    </row>
-    <row r="35" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J34" s="9"/>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" customHeight="1">
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -1396,20 +1490,21 @@
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
-    </row>
-    <row r="36" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:9" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:9" ht="15.75" customHeight="1"/>
+      <c r="J35" s="9"/>
+    </row>
+    <row r="36" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:10" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Penalty.xlsx
+++ b/JsonConverter/ExcelFiles/Penalty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\ACE\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F466FAD3-62D0-4775-8AE5-54A2A40FE379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B2A356E-A25B-4CC9-8D85-BDF4FBCF93EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16130" yWindow="1900" windowWidth="20870" windowHeight="11880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="12810" windowHeight="13935" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Penalty" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -397,6 +397,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD2F2DB"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor rgb="FF4D93D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor rgb="FF4D93D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor rgb="FFD86DCD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -447,7 +483,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -467,7 +503,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -476,6 +511,29 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -703,108 +761,108 @@
     <col min="3" max="3" width="24.7109375" style="2" customWidth="1"/>
     <col min="4" max="5" width="19.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="48.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" style="24" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="48.28515625" style="24" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="26.5703125" style="2" customWidth="1"/>
     <col min="12" max="16384" width="12.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="13" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:20" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="16" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="13" customFormat="1" ht="12.75">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:20" s="12" customFormat="1" ht="12.75">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="I2" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:20" s="15" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="14" t="s">
+      <c r="K2" s="11"/>
+    </row>
+    <row r="3" spans="1:20" s="14" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="I3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -818,7 +876,7 @@
       <c r="C4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="15" t="s">
         <v>49</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -827,16 +885,16 @@
       <c r="F4" s="3">
         <v>2</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="3">
+        <v>3</v>
+      </c>
+      <c r="H4" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="3">
+      <c r="I4" s="18">
         <v>10</v>
       </c>
-      <c r="I4" s="3">
-        <v>2</v>
-      </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="25" t="s">
         <v>61</v>
       </c>
       <c r="K4" s="10"/>
@@ -860,7 +918,7 @@
       <c r="C5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -869,16 +927,16 @@
       <c r="F5" s="3">
         <v>2</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="3">
+        <v>2</v>
+      </c>
+      <c r="H5" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="3">
+      <c r="I5" s="18">
         <v>10</v>
       </c>
-      <c r="I5" s="3">
-        <v>2</v>
-      </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="25" t="s">
         <v>62</v>
       </c>
       <c r="K5" s="4"/>
@@ -902,7 +960,7 @@
       <c r="C6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="15" t="s">
         <v>52</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -911,16 +969,16 @@
       <c r="F6" s="3">
         <v>2</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="3">
+        <v>2</v>
+      </c>
+      <c r="H6" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="3">
+      <c r="I6" s="18">
         <v>10</v>
       </c>
-      <c r="I6" s="3">
-        <v>2</v>
-      </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="18" t="s">
         <v>63</v>
       </c>
       <c r="K6" s="4"/>
@@ -953,16 +1011,16 @@
       <c r="F7" s="3">
         <v>2</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="3">
+        <v>3</v>
+      </c>
+      <c r="H7" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="3">
+      <c r="I7" s="18">
         <v>10</v>
       </c>
-      <c r="I7" s="3">
-        <v>2</v>
-      </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="18" t="s">
         <v>64</v>
       </c>
       <c r="K7" s="4"/>
@@ -995,16 +1053,16 @@
       <c r="F8" s="3">
         <v>2</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="3">
+        <v>4</v>
+      </c>
+      <c r="H8" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="18">
         <v>10</v>
       </c>
-      <c r="I8" s="3">
-        <v>2</v>
-      </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="18" t="s">
         <v>65</v>
       </c>
       <c r="K8" s="4"/>
@@ -1037,16 +1095,16 @@
       <c r="F9" s="3">
         <v>2</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="3">
+        <v>3</v>
+      </c>
+      <c r="H9" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="18">
         <v>10</v>
       </c>
-      <c r="I9" s="3">
-        <v>2</v>
-      </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="18" t="s">
         <v>66</v>
       </c>
       <c r="K9" s="4"/>
@@ -1079,16 +1137,16 @@
       <c r="F10" s="3">
         <v>2</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="3">
+        <v>4</v>
+      </c>
+      <c r="H10" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="18">
         <v>10</v>
       </c>
-      <c r="I10" s="3">
-        <v>2</v>
-      </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="18" t="s">
         <v>67</v>
       </c>
       <c r="K10" s="4"/>
@@ -1121,16 +1179,16 @@
       <c r="F11" s="1">
         <v>2</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="1">
+        <v>2</v>
+      </c>
+      <c r="H11" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="19">
         <v>10</v>
       </c>
-      <c r="I11" s="1">
-        <v>2</v>
-      </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="19" t="s">
         <v>68</v>
       </c>
       <c r="K11" s="4"/>
@@ -1163,16 +1221,16 @@
       <c r="F12" s="5">
         <v>2</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="5">
+        <v>4</v>
+      </c>
+      <c r="H12" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="5">
+      <c r="I12" s="20">
         <v>10</v>
       </c>
-      <c r="I12" s="5">
-        <v>2</v>
-      </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="20" t="s">
         <v>70</v>
       </c>
       <c r="K12" s="4"/>
@@ -1194,9 +1252,9 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
@@ -1216,9 +1274,9 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -1238,9 +1296,9 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -1260,9 +1318,9 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1">
       <c r="A17" s="7"/>
@@ -1272,9 +1330,9 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1">
       <c r="A18" s="7"/>
@@ -1284,9 +1342,9 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1">
       <c r="A19" s="7"/>
@@ -1296,9 +1354,9 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1">
       <c r="A20" s="7"/>
@@ -1308,9 +1366,9 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="7"/>
@@ -1320,9 +1378,9 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="7"/>
@@ -1332,9 +1390,9 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1">
       <c r="A23" s="7"/>
@@ -1344,9 +1402,9 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1">
       <c r="A24" s="7"/>
@@ -1356,9 +1414,9 @@
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1">
       <c r="A25" s="7"/>
@@ -1368,9 +1426,9 @@
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
@@ -1380,9 +1438,9 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
@@ -1392,9 +1450,9 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
@@ -1404,9 +1462,9 @@
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1">
       <c r="A29" s="8"/>
@@ -1416,9 +1474,9 @@
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1">
       <c r="A30" s="8"/>
@@ -1428,9 +1486,9 @@
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1">
       <c r="A31" s="8"/>
@@ -1440,9 +1498,9 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1">
       <c r="A32" s="9"/>
@@ -1452,9 +1510,9 @@
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="23"/>
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1">
       <c r="A33" s="9"/>
@@ -1464,9 +1522,9 @@
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
     </row>
     <row r="34" spans="1:10" ht="15.75" customHeight="1">
       <c r="A34" s="9"/>
@@ -1476,9 +1534,9 @@
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="23"/>
     </row>
     <row r="35" spans="1:10" ht="15.75" customHeight="1">
       <c r="A35" s="9"/>
@@ -1488,9 +1546,9 @@
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="23"/>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1"/>
     <row r="37" spans="1:10" ht="15.75" customHeight="1"/>
